--- a/data/trans_orig/IP07A06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A06-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31057</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13256</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24317</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19449</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41554</t>
+          <t>40646</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,52%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>26549</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>30184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46393</t>
+          <t>45404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33780</t>
+          <t>34654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,82 +1656,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>25068</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>18056</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>33145</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>10,53%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>13,93%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>50889</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>41087</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>62810</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>9,29%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>25068</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>18190</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33664</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>50889</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>41896</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>63260</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54025</t>
+          <t>55000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75762</t>
+          <t>75525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64783</t>
+          <t>64712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>87010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125380</t>
+          <t>125017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156331</t>
+          <t>156442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98863</t>
+          <t>98839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122560</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123148</t>
+          <t>125025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148231</t>
+          <t>147253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230283</t>
+          <t>230148</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>263145</t>
+          <t>261575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30087</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>27763</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26139</t>
+          <t>26850</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31949</t>
+          <t>31772</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49643</t>
+          <t>49232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38834</t>
+          <t>38672</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34889</t>
+          <t>34383</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51160</t>
+          <t>51787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69367</t>
+          <t>69884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39075</t>
+          <t>38552</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60542</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>37718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82495</t>
+          <t>82887</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112019</t>
+          <t>113846</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90872</t>
+          <t>91428</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118674</t>
+          <t>118506</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>96718</t>
+          <t>97381</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>124543</t>
+          <t>124045</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>197437</t>
+          <t>194048</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>235025</t>
+          <t>234489</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>144076</t>
+          <t>144292</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>173385</t>
+          <t>172651</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>170498</t>
+          <t>171628</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>201348</t>
+          <t>200630</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>324615</t>
+          <t>324441</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>364313</t>
+          <t>367843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24393</t>
+          <t>23942</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24228</t>
+          <t>24021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>28140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43591</t>
+          <t>43973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>18257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29791</t>
+          <t>29553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26982</t>
+          <t>26902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36357</t>
+          <t>36826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53261</t>
+          <t>52568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>16431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22620</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40248</t>
+          <t>39861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53905</t>
+          <t>53880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61462</t>
+          <t>61844</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87378</t>
+          <t>88120</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59203</t>
+          <t>59980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82037</t>
+          <t>82471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55036</t>
+          <t>55160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77058</t>
+          <t>76837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118861</t>
+          <t>121882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151746</t>
+          <t>152799</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82378</t>
+          <t>82848</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104575</t>
+          <t>106408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99724</t>
+          <t>101086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123769</t>
+          <t>125093</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188648</t>
+          <t>189540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225137</t>
+          <t>221762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20911</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36669</t>
+          <t>36930</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26024</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>24850</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46896</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34265</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18083</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29933</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42862</t>
+          <t>43565</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60849</t>
+          <t>61263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11219</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8639</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>44486</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67642</t>
+          <t>67694</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52652</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74825</t>
+          <t>76714</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>102382</t>
+          <t>103931</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>137366</t>
+          <t>136977</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94657</t>
+          <t>94143</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>121109</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87374</t>
+          <t>89127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115139</t>
+          <t>115975</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>191556</t>
+          <t>189301</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>228984</t>
+          <t>230097</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>130960</t>
+          <t>131178</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160358</t>
+          <t>160789</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>143328</t>
+          <t>142362</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>172865</t>
+          <t>171512</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>284481</t>
+          <t>281043</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>325194</t>
+          <t>322562</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>870</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15646</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>28037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>26415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43349</t>
+          <t>43713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26585</t>
+          <t>27882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>46067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>49864</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74621</t>
+          <t>74652</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61832</t>
+          <t>61688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86556</t>
+          <t>85440</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62828</t>
+          <t>62605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87356</t>
+          <t>86489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129980</t>
+          <t>130463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165109</t>
+          <t>165204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122406</t>
+          <t>122962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148943</t>
+          <t>148090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124613</t>
+          <t>124981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151432</t>
+          <t>151965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256439</t>
+          <t>254612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>291605</t>
+          <t>292274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>14365</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>27203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18769</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32378</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21990</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35516</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>44849</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64032</t>
+          <t>64498</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28986</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32320</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>47197</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>63913</t>
+          <t>64462</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85346</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42554</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>64711</t>
+          <t>65067</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>74868</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>103902</t>
+          <t>104570</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97099</t>
+          <t>97561</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126453</t>
+          <t>126715</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>96502</t>
+          <t>96617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126476</t>
+          <t>127728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>201075</t>
+          <t>203354</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>243919</t>
+          <t>244731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>169518</t>
+          <t>169591</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>201691</t>
+          <t>200138</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>182939</t>
+          <t>183255</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>215195</t>
+          <t>215066</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>361320</t>
+          <t>362627</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>407911</t>
+          <t>406179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse triste en 2023 (tasa de respuesta: 99,59%)</t>
+          <t>Menores según la frecuencia de sentirse triste, percibida por el adulto en 2023 (tasa de respuesta: 99,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>23914</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27816</t>
+          <t>28270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42936</t>
+          <t>43095</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22921</t>
+          <t>23155</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10039</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>32726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18311</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45473</t>
+          <t>47253</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69488</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56169</t>
+          <t>57591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90521</t>
+          <t>90508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98401</t>
+          <t>102270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147681</t>
+          <t>148672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168871</t>
+          <t>168260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207594</t>
+          <t>208024</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178723</t>
+          <t>177652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219003</t>
+          <t>219077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360360</t>
+          <t>358240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>418349</t>
+          <t>416369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>835</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20778</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>20427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>37516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50917</t>
+          <t>51313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64241</t>
+          <t>64829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70987</t>
+          <t>69913</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86143</t>
+          <t>85788</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126399</t>
+          <t>127197</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146954</t>
+          <t>147184</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,11%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30956</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32148</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37784</t>
+          <t>38816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25810</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46137</t>
+          <t>46320</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64178</t>
+          <t>66141</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54850</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88053</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76082</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112606</t>
+          <t>112341</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>138456</t>
+          <t>138418</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188247</t>
+          <t>189998</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>244233</t>
+          <t>245503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>286605</t>
+          <t>288172</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>274669</t>
+          <t>272431</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>319783</t>
+          <t>316742</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>530478</t>
+          <t>531507</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>591721</t>
+          <t>592532</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>
